--- a/data/Monday_Morning_Liquidity_Clean_Truth_Set.xlsx
+++ b/data/Monday_Morning_Liquidity_Clean_Truth_Set.xlsx
@@ -47,7 +47,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00186FAF"/>
+        <fgColor rgb="00156A9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -445,7 +445,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Synthetic demonstration data</t>
+          <t>Synthetic case</t>
         </is>
       </c>
     </row>
